--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Cedolino per dipendenti.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Cedolino per dipendenti.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
   <si>
     <r>
       <t xml:space="preserve">
@@ -400,7 +400,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -463,8 +463,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
-Per visualizzarlo, [visita questa pagina](URL).
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -474,7 +473,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -510,7 +509,6 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">.
-Per visualizzarla, [visita questa pagina](URL).
 </t>
     </r>
     <r>
@@ -520,7 +518,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -548,6 +546,12 @@
     <t>-</t>
   </si>
   <si>
+    <t>Scarica il cedolino</t>
+  </si>
+  <si>
+    <t>Scarica il documento</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -565,7 +569,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -630,10 +634,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
 </sst>
 </file>
@@ -1280,15 +1280,15 @@
         <v>69</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>53</v>
@@ -1302,58 +1302,58 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>69</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>53</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
